--- a/usd_krw_3y.xlsx
+++ b/usd_krw_3y.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="733">
   <si>
     <t>날짜</t>
   </si>
@@ -2210,6 +2210,9 @@
   </si>
   <si>
     <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
   </si>
 </sst>
 </file>
@@ -2383,9 +2386,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>USD_KRW_Data!$A$2:$A$730</c:f>
+              <c:f>USD_KRW_Data!$A$2:$A$731</c:f>
               <c:strCache>
-                <c:ptCount val="729"/>
+                <c:ptCount val="730"/>
                 <c:pt idx="0">
                   <c:v>2023-05-22</c:v>
                 </c:pt>
@@ -4572,16 +4575,19 @@
                 </c:pt>
                 <c:pt idx="728">
                   <c:v>2026-05-20</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>USD_KRW_Data!$B$2:$B$730</c:f>
+              <c:f>USD_KRW_Data!$B$2:$B$731</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="729"/>
+                <c:ptCount val="730"/>
                 <c:pt idx="0">
                   <c:v>1318.1</c:v>
                 </c:pt>
@@ -6768,6 +6774,9 @@
                 </c:pt>
                 <c:pt idx="728">
                   <c:v>1506.8</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>1506.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6908,9 +6917,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>USD_KRW_Data!$A$2:$A$730</c:f>
+              <c:f>USD_KRW_Data!$A$2:$A$731</c:f>
               <c:strCache>
-                <c:ptCount val="729"/>
+                <c:ptCount val="730"/>
                 <c:pt idx="0">
                   <c:v>2023-05-22</c:v>
                 </c:pt>
@@ -9097,16 +9106,19 @@
                 </c:pt>
                 <c:pt idx="728">
                   <c:v>2026-05-20</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>USD_KRW_Data!$C$2:$C$730</c:f>
+              <c:f>USD_KRW_Data!$C$2:$C$731</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="729"/>
+                <c:ptCount val="730"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11292,7 +11304,10 @@
                   <c:v>1508.7</c:v>
                 </c:pt>
                 <c:pt idx="728">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>1496.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11727,7 +11742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C730"/>
+  <dimension ref="A1:C731"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -19219,8 +19234,19 @@
       <c r="B730" s="3">
         <v>1506.8</v>
       </c>
-      <c r="C730" s="4">
-        <v>1508.7</v>
+      <c r="C730" s="3">
+        <v>1496.7</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3">
+      <c r="A731" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B731" s="3">
+        <v>1506.1</v>
+      </c>
+      <c r="C731" s="4">
+        <v>1496.7</v>
       </c>
     </row>
   </sheetData>
